--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1911</v>
+        <v>85013.49000000001</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>966</v>
+        <v>42973.85</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>613.1118</v>
+        <v>27275.13</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>207.111</v>
+        <v>9213.620000000001</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>167.4</v>
+        <v>7447.02</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>982.3</v>
+        <v>43698.98</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>258.9678</v>
+        <v>11520.54</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>17221.9656</v>
+        <v>766143.0699999999</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1061.718</v>
+        <v>47232</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>924.6</v>
+        <v>41132.12</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9383.6073</v>
+        <v>417442.81</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>241.5861</v>
+        <v>10747.29</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>490.8447</v>
+        <v>21835.91</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1268.8732</v>
+        <v>56447.59</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>466.8474</v>
+        <v>20768.36</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>424.3008</v>
+        <v>18875.61</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>367.35</v>
+        <v>16342.08</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>884.5248</v>
+        <v>39349.31</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5538.7969</v>
+        <v>246401.07</v>
       </c>
     </row>
     <row r="21">
@@ -1724,17 +1724,17 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1598.8496</v>
+        <v>71127.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1588-70-CM26</t>
+          <t>5647-66-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,22 +1749,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,28 +1774,28 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ACS INGENIEROS SPA</t>
+          <t>NETICS SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.240.927-5</t>
+          <t>76.363.873-1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>468.72</v>
+        <v>13584.72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5647-66-CM26</t>
+          <t>598-17-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,53 +1810,53 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.513.000-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NETICS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.363.873-1</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>305.368</v>
+        <v>48135.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>598-17-CM26</t>
+          <t>4295-32-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,48 +1876,48 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1082.035</v>
+        <v>69500.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4295-32-CM26</t>
+          <t>1093219-8-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,43 +1942,43 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>GRUPO 5 SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.024.553-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1562.28</v>
+        <v>64701.81</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1093219-8-CM26</t>
+          <t>4473-151-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,53 +1993,53 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>GRUPO 5 SPA</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.024.553-4</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1454.418</v>
+        <v>10503.61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4473-151-CM26</t>
+          <t>1614-6-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,43 +2064,43 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.100.200-4</t>
+          <t>60.510.000-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+          <t>Superintendencia de Electricidad y Combustibles</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>SOAINT GESTION S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>96.829.360-5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>236.1084</v>
+        <v>60879.62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1614-6-CM26</t>
+          <t>1480065-3-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,22 +2115,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Superintendencia de Electricidad y Combustibles</t>
+          <t>MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,28 +2140,28 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SOAINT GESTION S.A.</t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.829.360-5</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1368.5</v>
+        <v>28960.64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1480065-3-CM26</t>
+          <t>1725-267-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,53 +2176,53 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
+          <t>77.714.387-5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>651</v>
+        <v>72797.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1725-267-CM26</t>
+          <t>1057539-2804-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,53 +2237,53 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1636.39</v>
+        <v>386079.54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057539-2804-CM26</t>
+          <t>2581-5-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,43 +2308,43 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>69.070.200-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE CONCHALI</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8678.599200000001</v>
+        <v>33506.77</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2581-5-CM26</t>
+          <t>1186229-57-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.070.200-2</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCHALI</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,28 +2384,28 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>753.1915</v>
+        <v>676558.0699999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1186229-57-CM26</t>
+          <t>5403-17-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>61.978.810-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>COMISION NACIONAL DE ACREDITACION</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,28 +2445,28 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>LIVISTER CHILE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>77.622.841-9</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>15208.2036</v>
+        <v>203660.91</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5403-17-CM26</t>
+          <t>1093219-9-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,28 +2506,28 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>LIVISTER CHILE SPA</t>
+          <t>Seidor Chile S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.622.841-9</t>
+          <t>96.986.170-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4578.05</v>
+        <v>69732.42</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1093219-9-CM26</t>
+          <t>770-51-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.604.000-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Dirección Nacional de Fronteras y Límites del Esta</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,28 +2567,28 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Seidor Chile S.A.</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.986.170-4</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1567.5</v>
+        <v>84032.19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>770-51-CM26</t>
+          <t>621923-19-SE26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.604.000-8</t>
+          <t>53.314.945-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dirección Nacional de Fronteras y Límites del Esta</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,28 +2628,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+          <t>SOFTGROUP SERVICIOS COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.083.021-6</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>77.388.870-1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1888.9416</v>
+        <v>68820.44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>621923-19-SE26</t>
+          <t>2109-868-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2674,12 +2678,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>53.314.945-6</t>
+          <t>61.608.203-5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,32 +2693,28 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SOFTGROUP SERVICIOS COMPUTACIONALES LIMITADA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.388.870-1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1547</v>
+        <v>46501.24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2109-868-CM26</t>
+          <t>1305504-68-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2734,103 +2734,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.608.203-5</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>DISEÑO Y DESARROLLO VISUALMENTE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.046.871-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1045.2914</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>1305504-68-CM26</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>61.981.100-3</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bío-Bío</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>DISEÑO Y DESARROLLO VISUALMENTE SPA</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>76.046.871-1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>CLF</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>441</v>
+        <v>19618.5</v>
       </c>
     </row>
   </sheetData>
